--- a/reports/Leetcode Daily Report 3 year_2026-09-19.xlsx
+++ b/reports/Leetcode Daily Report 3 year_2026-09-19.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>52</v>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44">
@@ -1637,7 +1637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1887,7 +1887,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M JESIN MILESH</t>
+          <t>LIYAS ALI N</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MANDA MANOJ KUMAR.M</t>
+          <t>M JESIN MILESH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MANNEM PUSHPA LATHA</t>
+          <t>MANDA MANOJ KUMAR.M</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1923,7 +1923,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MONEESH KUMAR T</t>
+          <t>MANNEM PUSHPA LATHA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1935,7 +1935,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MUNAGALA KUNDANA</t>
+          <t>MONEESH KUMAR T</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1947,7 +1947,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NALLAPANENI ANJANEYULU</t>
+          <t>MUNAGALA KUNDANA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1959,7 +1959,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NATAKARANI VYSHNAVI</t>
+          <t>NALLAPANENI ANJANEYULU</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1971,7 +1971,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NAYUNIPATI MOKSHESWARA</t>
+          <t>NATAKARANI VYSHNAVI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1983,7 +1983,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NITHILA S</t>
+          <t>NAYUNIPATI MOKSHESWARA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1995,7 +1995,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PODIKITI VARSHANJALI</t>
+          <t>NITHILA S</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2007,7 +2007,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>POOLA HASINI</t>
+          <t>PODIKITI VARSHANJALI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PRIYA G</t>
+          <t>POOLA HASINI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2031,7 +2031,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PUVADDA ARAVIND SUBASH</t>
+          <t>PRIYA G</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2043,7 +2043,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PYDIPATI YASWANTH</t>
+          <t>PUVADDA ARAVIND SUBASH</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2055,7 +2055,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RAGHUL J</t>
+          <t>PYDIPATI YASWANTH</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2067,7 +2067,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RAKSHITHA V</t>
+          <t>RAGHUL J</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2079,7 +2079,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RAMAMOORTHY H</t>
+          <t>RAKSHITHA V</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2091,7 +2091,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S.C LEELA KRISHNA VARMA</t>
+          <t>RAMAMOORTHY H</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2103,7 +2103,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SHAIK ASHWAQ AHMED</t>
+          <t>S.C LEELA KRISHNA VARMA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2115,7 +2115,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SOORYA. G. D</t>
+          <t>SHAIK ASHWAQ AHMED</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2127,7 +2127,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SUJITH KUMAR D</t>
+          <t>SOORYA. G. D</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>THIRUSELVEN P</t>
+          <t>SUJITH KUMAR D</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2151,10 +2151,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>THIRUSELVEN P</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>YUTHISH S</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
         </is>

--- a/reports/Leetcode Daily Report 3 year_2026-09-19.xlsx
+++ b/reports/Leetcode Daily Report 3 year_2026-09-19.xlsx
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>9</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10">
@@ -1023,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25">
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37">
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48">
@@ -1637,7 +1637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1743,7 +1743,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CHERUKURU THANUJA</t>
+          <t>CHARAN SAI PATHAPATHI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DANTLA MEGHANA REDDY</t>
+          <t>CHERUKURU THANUJA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1767,7 +1767,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DEVIREDDY YASWANTH KUMAR REDDY</t>
+          <t>DANTLA MEGHANA REDDY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1779,7 +1779,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DODLA VENKATA MOKSHITH</t>
+          <t>DEVIREDDY YASWANTH KUMAR REDDY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1791,7 +1791,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PRAJESH G</t>
+          <t>DODLA VENKATA MOKSHITH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GOPANAPALLI KOUSTHUBA</t>
+          <t>PRAJESH G</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1815,7 +1815,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GUMPARLAPATI VENKATA SAI KRISHNA</t>
+          <t>GOPANAPALLI KOUSTHUBA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1827,7 +1827,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HARSHITHA B</t>
+          <t>GUMPARLAPATI VENKATA SAI KRISHNA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1839,7 +1839,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HEMASRI R</t>
+          <t>HARSHITHA B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1851,7 +1851,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KATTABATTHINA SAI MANI</t>
+          <t>HEMASRI R</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KOMMINENI SATHEESH KUMAR</t>
+          <t>KATTABATTHINA SAI MANI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1875,7 +1875,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KUSETTY NIHARIKA</t>
+          <t>KOMMINENI SATHEESH KUMAR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1887,7 +1887,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LIYAS ALI N</t>
+          <t>KUSETTY NIHARIKA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M JESIN MILESH</t>
+          <t>LIYAS ALI N</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MANDA MANOJ KUMAR.M</t>
+          <t>LOHITH D</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1923,7 +1923,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MANNEM PUSHPA LATHA</t>
+          <t>M JESIN MILESH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1935,7 +1935,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MONEESH KUMAR T</t>
+          <t>MANDA MANOJ KUMAR.M</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1947,7 +1947,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MUNAGALA KUNDANA</t>
+          <t>MANNEM PUSHPA LATHA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1959,7 +1959,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NALLAPANENI ANJANEYULU</t>
+          <t>MONEESH KUMAR T</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1971,7 +1971,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NATAKARANI VYSHNAVI</t>
+          <t>MUNAGALA KUNDANA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1983,7 +1983,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NAYUNIPATI MOKSHESWARA</t>
+          <t>NALLAPANENI ANJANEYULU</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1995,7 +1995,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NITHILA S</t>
+          <t>NATAKARANI VYSHNAVI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2007,7 +2007,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PODIKITI VARSHANJALI</t>
+          <t>NAYUNIPATI MOKSHESWARA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>POOLA HASINI</t>
+          <t>NITHILA S</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2031,7 +2031,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PRIYA G</t>
+          <t>PODIKITI VARSHANJALI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2043,7 +2043,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PUVADDA ARAVIND SUBASH</t>
+          <t>POOLA HASINI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2055,7 +2055,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PYDIPATI YASWANTH</t>
+          <t>PRAVEEN KUMAR.S</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2067,7 +2067,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RAGHUL J</t>
+          <t>PRIYA G</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2079,7 +2079,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RAKSHITHA V</t>
+          <t>PUVADDA ARAVIND SUBASH</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2091,7 +2091,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RAMAMOORTHY H</t>
+          <t>PYDIPATI YASWANTH</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2103,7 +2103,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S.C LEELA KRISHNA VARMA</t>
+          <t>RAGHUL J</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2115,7 +2115,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SHAIK ASHWAQ AHMED</t>
+          <t>RAKSHITHA V</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2127,7 +2127,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SOORYA. G. D</t>
+          <t>RAMAMOORTHY H</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SUJITH KUMAR D</t>
+          <t>S.C LEELA KRISHNA VARMA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2151,7 +2151,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>THIRUSELVEN P</t>
+          <t>SHAIK ASHWAQ AHMED</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2163,10 +2163,58 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>SOORYA. G. D</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SUJITH KUMAR D</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SURENDHAR B</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>THIRUSELVEN P</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>YUTHISH S</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Recent-activity window is full (20 entries) -- today's count may be a lower bound</t>
         </is>
